--- a/data/trans_camb/P43-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43-Clase-trans_camb.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,9 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,25 +526,18 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Hombre</t>
+          <t>Mujer</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Mujer</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -578,21 +568,6 @@
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2023/2007</t>
         </is>
@@ -607,9 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -624,17 +596,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-2,98</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3,31</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,21</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -648,21 +620,6 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>15,21</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-2,98</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3,31</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15,21</t>
         </is>
@@ -677,47 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-11,46; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,5; 11,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,1; 22,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 5,5</t>
+          <t>-11,46; 4,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 12,01</t>
+          <t>-4,5; 11,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 22,25</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-11,14; 5,5</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-4,28; 12,01</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>7,34; 22,25</t>
+          <t>8,1; 22,55</t>
         </is>
       </c>
     </row>
@@ -730,17 +672,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-6,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,21 +696,6 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>33,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-6,47%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7,19%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>33,01%</t>
         </is>
@@ -783,47 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,84; 11,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,76; 27,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16,09; 53,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 12,97</t>
+          <t>-22,84; 11,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 28,91</t>
+          <t>-8,76; 27,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 52,94</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-22,32; 12,97</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-8,47; 28,91</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14,28; 52,94</t>
+          <t>16,09; 53,94</t>
         </is>
       </c>
     </row>
@@ -840,17 +752,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,45</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28,86</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -864,21 +776,6 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,86</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>15,45</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28,86</t>
         </is>
@@ -893,47 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,71; 15,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,45; 22,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>21,6; 35,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 15,63</t>
+          <t>0,71; 15,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,14; 22,96</t>
+          <t>8,45; 22,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,31; 35,72</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,07; 15,63</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>8,14; 22,96</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>21,31; 35,72</t>
+          <t>21,6; 35,6</t>
         </is>
       </c>
     </row>
@@ -946,17 +828,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -970,21 +852,6 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>92,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>92,57%</t>
         </is>
@@ -999,47 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,8; 55,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,75; 84,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61,1; 129,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,11; 55,07</t>
+          <t>1,8; 55,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 82,16</t>
+          <t>24,75; 84,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,44; 128,94</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 55,07</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22,8; 82,16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62,44; 128,94</t>
+          <t>61,1; 129,6</t>
         </is>
       </c>
     </row>
@@ -1056,17 +908,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,02</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14,9</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23,42</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1080,21 +932,6 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>23,42</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,02</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>14,9</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>23,42</t>
         </is>
@@ -1109,47 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,78; 20,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,2; 25,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11,27; 33,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 20,54</t>
+          <t>0,78; 20,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 25,45</t>
+          <t>3,2; 25,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,39; 33,88</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,8; 20,54</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4,16; 25,45</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12,39; 33,88</t>
+          <t>11,27; 33,21</t>
         </is>
       </c>
     </row>
@@ -1162,17 +984,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1186,21 +1008,6 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>57,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,84%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>36,28%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>57,03%</t>
         </is>
@@ -1215,47 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,72; 59,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,23; 73,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,86; 94,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 58,39</t>
+          <t>1,72; 59,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,1; 71,37</t>
+          <t>7,23; 73,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,72; 94,54</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,49; 58,39</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>9,1; 71,37</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>25,72; 94,54</t>
+          <t>24,86; 94,67</t>
         </is>
       </c>
     </row>
@@ -1272,17 +1064,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6,34</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>29,63</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1296,21 +1088,6 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,63</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,34</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7,82</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>29,63</t>
         </is>
@@ -1325,47 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,23; 11,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,07; 12,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,56; 49,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 12,06</t>
+          <t>1,23; 11,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,44</t>
+          <t>3,07; 12,71</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,36; 52,72</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,53; 12,06</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3,1; 13,44</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>14,36; 52,72</t>
+          <t>14,56; 49,72</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1140,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1402,21 +1164,6 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>19,01%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>88,87%</t>
         </is>
@@ -1431,47 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>3,49; 36,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8,44; 41,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,77; 162,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 38,82</t>
+          <t>3,49; 36,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 43,6</t>
+          <t>8,44; 41,57</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,26; 165,4</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,65; 38,82</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>8,38; 43,6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>41,26; 165,4</t>
+          <t>41,77; 162,4</t>
         </is>
       </c>
     </row>
@@ -1488,17 +1220,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15,52</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20,73</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16,11</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1512,21 +1244,6 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,11</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>15,52</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20,73</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>16,11</t>
         </is>
@@ -1541,47 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>10,73; 21,03</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,36; 26,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,98; 24,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,01; 21,04</t>
+          <t>10,73; 21,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,18; 26,55</t>
+          <t>15,36; 26,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 24,97</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>10,01; 21,04</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>15,18; 26,55</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>-0,01; 24,97</t>
+          <t>-0,98; 24,42</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1296,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>57,4%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1618,21 +1320,6 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>42,98%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>57,4%</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>44,61%</t>
         </is>
@@ -1647,47 +1334,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,56; 64,07</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,63; 78,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,79; 71,62</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25,55; 64,35</t>
+          <t>27,56; 64,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,99; 81,08</t>
+          <t>38,63; 78,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,38; 73,18</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>25,55; 64,35</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>38,99; 81,08</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 73,18</t>
+          <t>-1,79; 71,62</t>
         </is>
       </c>
     </row>
@@ -1704,17 +1376,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,74</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>11,43</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5,26</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1728,21 +1400,6 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>10,74</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>11,43</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>5,26</t>
         </is>
@@ -1757,47 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,56; 14,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,65; 15,48</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,93; 10,01</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,52; 15,16</t>
+          <t>6,56; 14,94</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,81; 15,35</t>
+          <t>7,65; 15,48</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,57; 9,95</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>6,52; 15,16</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6,81; 15,35</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>0,57; 9,95</t>
+          <t>0,93; 10,01</t>
         </is>
       </c>
     </row>
@@ -1810,17 +1452,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1834,21 +1476,6 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>12,84%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>26,22%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>27,9%</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>12,84%</t>
         </is>
@@ -1863,47 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15,45; 38,22</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,85; 39,85</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,36; 25,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,11; 38,99</t>
+          <t>15,45; 38,22</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>16,01; 39,49</t>
+          <t>17,85; 39,85</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1,72; 25,12</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>15,11; 38,99</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>16,01; 39,49</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 25,12</t>
+          <t>2,36; 25,58</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1532,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9,23</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12,03</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18,24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1944,21 +1556,6 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>18,24</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9,23</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>12,03</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>18,24</t>
         </is>
@@ -1973,47 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>6,78; 11,42</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,67; 14,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13,29; 29,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,54</t>
+          <t>6,78; 11,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,74; 14,4</t>
+          <t>9,67; 14,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,02; 27,73</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6,72; 11,54</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>9,74; 14,4</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>13,02; 27,73</t>
+          <t>13,29; 29,12</t>
         </is>
       </c>
     </row>
@@ -2026,17 +1608,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2050,21 +1632,6 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>48,11%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>24,35%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>31,73%</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>48,11%</t>
         </is>
@@ -2079,47 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,42; 30,97</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,7; 39,01</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,58; 77,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,06; 31,5</t>
+          <t>17,42; 30,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,75; 39,06</t>
+          <t>24,7; 39,01</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>33,83; 75,25</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>17,06; 31,5</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>24,75; 39,06</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>33,83; 75,25</t>
+          <t>34,58; 77,33</t>
         </is>
       </c>
     </row>
@@ -2131,13 +1683,12 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A11"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A12:A15"/>
-    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>

--- a/data/trans_camb/P43-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P43-Clase-trans_camb.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15,21</t>
+          <t>15,82</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,21</t>
+          <t>15,82</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 4,98</t>
+          <t>-11,17; 5,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 11,47</t>
+          <t>-4,74; 10,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 22,55</t>
+          <t>9,09; 22,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 4,98</t>
+          <t>-11,17; 5,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 11,47</t>
+          <t>-4,74; 10,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,1; 22,55</t>
+          <t>9,09; 22,85</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,34%</t>
         </is>
       </c>
     </row>
@@ -710,32 +710,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 11,65</t>
+          <t>-22,05; 12,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 27,77</t>
+          <t>-9,55; 25,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 53,94</t>
+          <t>17,93; 55,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 11,65</t>
+          <t>-22,05; 12,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 27,77</t>
+          <t>-9,55; 25,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,09; 53,94</t>
+          <t>17,93; 55,62</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>28,86</t>
+          <t>28,42</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,86</t>
+          <t>28,42</t>
         </is>
       </c>
     </row>
@@ -790,32 +790,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 15,28</t>
+          <t>0,54; 15,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 22,75</t>
+          <t>8,28; 22,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 35,6</t>
+          <t>20,9; 35,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 15,28</t>
+          <t>0,54; 15,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,45; 22,75</t>
+          <t>8,28; 22,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 35,6</t>
+          <t>20,9; 35,47</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -866,32 +866,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 55,3</t>
+          <t>2,43; 57,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,75; 84,42</t>
+          <t>22,97; 83,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,1; 129,6</t>
+          <t>60,03; 130,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 55,3</t>
+          <t>2,43; 57,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,75; 84,42</t>
+          <t>22,97; 83,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,1; 129,6</t>
+          <t>60,03; 130,0</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,42</t>
+          <t>21,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,42</t>
+          <t>21,35</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 20,83</t>
+          <t>1,71; 20,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 25,6</t>
+          <t>3,34; 25,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 33,21</t>
+          <t>9,86; 32,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 20,83</t>
+          <t>1,71; 20,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,2; 25,6</t>
+          <t>3,34; 25,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,27; 33,21</t>
+          <t>9,86; 32,16</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -1022,32 +1022,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 59,89</t>
+          <t>3,68; 56,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 73,23</t>
+          <t>6,82; 70,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24,86; 94,67</t>
+          <t>20,52; 89,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,72; 59,89</t>
+          <t>3,68; 56,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,23; 73,23</t>
+          <t>6,82; 70,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,86; 94,67</t>
+          <t>20,52; 89,22</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29,63</t>
+          <t>14,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,63</t>
+          <t>14,91</t>
         </is>
       </c>
     </row>
@@ -1102,32 +1102,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,24</t>
+          <t>1,04; 11,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,71</t>
+          <t>2,45; 12,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 49,72</t>
+          <t>9,73; 19,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,24</t>
+          <t>1,04; 11,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,07; 12,71</t>
+          <t>2,45; 12,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,56; 49,72</t>
+          <t>9,73; 19,76</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>44,7%</t>
         </is>
       </c>
     </row>
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 36,66</t>
+          <t>2,52; 36,8</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 41,57</t>
+          <t>6,66; 40,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,77; 162,4</t>
+          <t>27,42; 62,84</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,49; 36,66</t>
+          <t>2,52; 36,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,44; 41,57</t>
+          <t>6,66; 40,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,77; 162,4</t>
+          <t>27,42; 62,84</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>17,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,11</t>
+          <t>17,83</t>
         </is>
       </c>
     </row>
@@ -1258,32 +1258,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>10,73; 21,03</t>
+          <t>10,42; 21,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,36; 26,24</t>
+          <t>15,42; 26,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 24,42</t>
+          <t>12,79; 23,18</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10,73; 21,03</t>
+          <t>10,42; 21,48</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,36; 26,24</t>
+          <t>15,42; 26,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 24,42</t>
+          <t>12,79; 23,18</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1334,39 +1334,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,56; 64,07</t>
+          <t>26,76; 66,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>38,63; 78,3</t>
+          <t>39,51; 81,64</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 71,62</t>
+          <t>32,58; 70,27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27,56; 64,07</t>
+          <t>26,76; 66,15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>38,63; 78,3</t>
+          <t>39,51; 81,64</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 71,62</t>
+          <t>32,58; 70,27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>4,31</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,26</t>
+          <t>4,31</t>
         </is>
       </c>
     </row>
@@ -1414,32 +1414,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,94</t>
+          <t>7,0; 15,02</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,48</t>
+          <t>7,18; 15,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,01</t>
+          <t>-0,1; 8,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6,56; 14,94</t>
+          <t>7,0; 15,02</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,48</t>
+          <t>7,18; 15,76</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,01</t>
+          <t>-0,1; 8,87</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -1490,32 +1490,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>15,45; 38,22</t>
+          <t>16,35; 38,52</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>17,85; 39,85</t>
+          <t>16,88; 40,49</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2,36; 25,58</t>
+          <t>-0,26; 22,43</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>15,45; 38,22</t>
+          <t>16,35; 38,52</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>17,85; 39,85</t>
+          <t>16,88; 40,49</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,36; 25,58</t>
+          <t>-0,26; 22,43</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18,24</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,24</t>
+          <t>14,59</t>
         </is>
       </c>
     </row>
@@ -1570,32 +1570,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,42</t>
+          <t>6,93; 11,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>9,67; 14,27</t>
+          <t>9,83; 14,63</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13,29; 29,12</t>
+          <t>12,36; 16,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,78; 11,42</t>
+          <t>6,93; 11,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>9,67; 14,27</t>
+          <t>9,83; 14,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,29; 29,12</t>
+          <t>12,36; 16,98</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -1646,32 +1646,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,42; 30,97</t>
+          <t>17,94; 32,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24,7; 39,01</t>
+          <t>25,2; 39,93</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34,58; 77,33</t>
+          <t>31,65; 46,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,42; 30,97</t>
+          <t>17,94; 32,26</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>24,7; 39,01</t>
+          <t>25,2; 39,93</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>34,58; 77,33</t>
+          <t>31,65; 46,77</t>
         </is>
       </c>
     </row>
